--- a/北京中心-顾问薪酬绩效台账.xlsx
+++ b/北京中心-顾问薪酬绩效台账.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集训营" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="走读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四六级" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个性化" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="在职研" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英学" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="集训营" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="走读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="四六级" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="个性化" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="在职研" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="英学" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'集训营'!$A$2:$AA$145</definedName>
@@ -28,10 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -613,8 +612,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="顾问业绩奖金及绩效"/>
       <sheetName val="业绩奖金"/>
@@ -852,8 +851,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="顾问业绩奖金及绩效"/>
       <sheetName val="业绩奖金"/>
@@ -41360,30 +41359,84 @@
       <c r="AO14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="M15" s="16" t="n"/>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="16" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="24" t="n"/>
-      <c r="R15" s="16" t="n"/>
-      <c r="S15" s="16" t="n"/>
-      <c r="T15" s="16" t="n"/>
-      <c r="U15" s="16" t="n"/>
-      <c r="V15" s="16" t="n"/>
-      <c r="W15" s="16" t="n"/>
-      <c r="X15" s="16" t="n"/>
+      <c r="A15" s="77" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B15" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D15" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E15" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F15" s="73">
+        <f>G15+H15</f>
+        <v/>
+      </c>
+      <c r="G15" s="73" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H15" s="73">
+        <f>R15</f>
+        <v/>
+      </c>
+      <c r="I15" s="73" t="n">
+        <v>190000</v>
+      </c>
+      <c r="J15" s="73" t="n">
+        <v>188700</v>
+      </c>
+      <c r="K15" s="73" t="n">
+        <v>61647.6</v>
+      </c>
+      <c r="L15" s="73" t="n">
+        <v>127052.4</v>
+      </c>
+      <c r="M15" s="74" t="n">
+        <v>0.874867894736842</v>
+      </c>
+      <c r="N15" s="73" t="n">
+        <v>45390</v>
+      </c>
+      <c r="O15" s="73" t="n">
+        <v>6217.5</v>
+      </c>
+      <c r="P15" s="73" t="n">
+        <v>39172.5</v>
+      </c>
+      <c r="Q15" s="75" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R15" s="73" t="n">
+        <v>5817.8715</v>
+      </c>
+      <c r="S15" s="73" t="n">
+        <v>71</v>
+      </c>
+      <c r="T15" s="74" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U15" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V15" s="73" t="n">
+        <v>1420</v>
+      </c>
+      <c r="W15" s="72" t="n"/>
+      <c r="X15" s="72" t="n"/>
       <c r="Y15" s="16" t="n"/>
       <c r="Z15" s="16" t="n"/>
       <c r="AA15" s="16" t="n"/>
@@ -41403,30 +41456,84 @@
       <c r="AO15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="24" t="n"/>
-      <c r="R16" s="16" t="n"/>
-      <c r="S16" s="16" t="n"/>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="16" t="n"/>
-      <c r="V16" s="16" t="n"/>
-      <c r="W16" s="16" t="n"/>
-      <c r="X16" s="16" t="n"/>
+      <c r="A16" s="77" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B16" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D16" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E16" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F16" s="73">
+        <f>G16+H16</f>
+        <v/>
+      </c>
+      <c r="G16" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H16" s="73">
+        <f>R16</f>
+        <v/>
+      </c>
+      <c r="I16" s="73" t="n">
+        <v>190000</v>
+      </c>
+      <c r="J16" s="73" t="n">
+        <v>201800</v>
+      </c>
+      <c r="K16" s="73" t="n">
+        <v>91039.3</v>
+      </c>
+      <c r="L16" s="73" t="n">
+        <v>110760.7</v>
+      </c>
+      <c r="M16" s="74" t="n">
+        <v>0.844101052631579</v>
+      </c>
+      <c r="N16" s="73" t="n">
+        <v>49618.5</v>
+      </c>
+      <c r="O16" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="73" t="n">
+        <v>49618.5</v>
+      </c>
+      <c r="Q16" s="75" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R16" s="73" t="n">
+        <v>5613.272</v>
+      </c>
+      <c r="S16" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V16" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W16" s="72" t="n"/>
+      <c r="X16" s="72" t="n"/>
       <c r="Y16" s="16" t="n"/>
       <c r="Z16" s="16" t="n"/>
       <c r="AA16" s="16" t="n"/>
@@ -41446,30 +41553,86 @@
       <c r="AO16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="24" t="n"/>
-      <c r="R17" s="16" t="n"/>
-      <c r="S17" s="16" t="n"/>
-      <c r="T17" s="16" t="n"/>
-      <c r="U17" s="16" t="n"/>
-      <c r="V17" s="16" t="n"/>
-      <c r="W17" s="16" t="n"/>
-      <c r="X17" s="16" t="n"/>
+      <c r="A17" s="77" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B17" s="72" t="inlineStr">
+        <is>
+          <t>王沛贤</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D17" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E17" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F17" s="73">
+        <f>G17+H17</f>
+        <v/>
+      </c>
+      <c r="G17" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H17" s="73">
+        <f>R17</f>
+        <v/>
+      </c>
+      <c r="I17" s="73" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="74" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="N17" s="73" t="n">
+        <v>2786</v>
+      </c>
+      <c r="O17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="73" t="n">
+        <v>2786</v>
+      </c>
+      <c r="Q17" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T17" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V17" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W17" s="72" t="n"/>
+      <c r="X17" s="72" t="n"/>
       <c r="Y17" s="16" t="n"/>
       <c r="Z17" s="16" t="n"/>
       <c r="AA17" s="16" t="n"/>

--- a/北京中心-顾问薪酬绩效台账.xlsx
+++ b/北京中心-顾问薪酬绩效台账.xlsx
@@ -41652,30 +41652,84 @@
       <c r="AO17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="24" t="n"/>
-      <c r="R18" s="16" t="n"/>
-      <c r="S18" s="16" t="n"/>
-      <c r="T18" s="16" t="n"/>
-      <c r="U18" s="16" t="n"/>
-      <c r="V18" s="16" t="n"/>
-      <c r="W18" s="16" t="n"/>
-      <c r="X18" s="16" t="n"/>
+      <c r="A18" s="77" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B18" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D18" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E18" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F18" s="73">
+        <f>G18+H18</f>
+        <v/>
+      </c>
+      <c r="G18" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H18" s="73">
+        <f>R18</f>
+        <v/>
+      </c>
+      <c r="I18" s="73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J18" s="73" t="n">
+        <v>272780</v>
+      </c>
+      <c r="K18" s="73" t="n">
+        <v>62431.4</v>
+      </c>
+      <c r="L18" s="73" t="n">
+        <v>210348.6</v>
+      </c>
+      <c r="M18" s="74" t="n">
+        <v>1.20403583333333</v>
+      </c>
+      <c r="N18" s="73" t="n">
+        <v>90005</v>
+      </c>
+      <c r="O18" s="73" t="n">
+        <v>11385</v>
+      </c>
+      <c r="P18" s="73" t="n">
+        <v>78620</v>
+      </c>
+      <c r="Q18" s="75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R18" s="73" t="n">
+        <v>17338.116</v>
+      </c>
+      <c r="S18" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V18" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W18" s="72" t="n"/>
+      <c r="X18" s="72" t="n"/>
       <c r="Y18" s="16" t="n"/>
       <c r="Z18" s="16" t="n"/>
       <c r="AA18" s="16" t="n"/>
@@ -41695,30 +41749,84 @@
       <c r="AO18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="24" t="n"/>
-      <c r="R19" s="16" t="n"/>
-      <c r="S19" s="16" t="n"/>
-      <c r="T19" s="16" t="n"/>
-      <c r="U19" s="16" t="n"/>
-      <c r="V19" s="16" t="n"/>
-      <c r="W19" s="16" t="n"/>
-      <c r="X19" s="16" t="n"/>
+      <c r="A19" s="77" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B19" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D19" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E19" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F19" s="73">
+        <f>G19+H19</f>
+        <v/>
+      </c>
+      <c r="G19" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H19" s="73">
+        <f>R19</f>
+        <v/>
+      </c>
+      <c r="I19" s="73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J19" s="73" t="n">
+        <v>223500</v>
+      </c>
+      <c r="K19" s="73" t="n">
+        <v>56320.6</v>
+      </c>
+      <c r="L19" s="73" t="n">
+        <v>167179.4</v>
+      </c>
+      <c r="M19" s="74" t="n">
+        <v>1.25185979166667</v>
+      </c>
+      <c r="N19" s="73" t="n">
+        <v>144521.95</v>
+      </c>
+      <c r="O19" s="73" t="n">
+        <v>11255</v>
+      </c>
+      <c r="P19" s="73" t="n">
+        <v>133266.95</v>
+      </c>
+      <c r="Q19" s="75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R19" s="73" t="n">
+        <v>18026.781</v>
+      </c>
+      <c r="S19" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V19" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W19" s="72" t="n"/>
+      <c r="X19" s="72" t="n"/>
       <c r="Y19" s="16" t="n"/>
       <c r="Z19" s="16" t="n"/>
       <c r="AA19" s="16" t="n"/>
@@ -41738,30 +41846,84 @@
       <c r="AO19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="24" t="n"/>
-      <c r="R20" s="16" t="n"/>
-      <c r="S20" s="16" t="n"/>
-      <c r="T20" s="16" t="n"/>
-      <c r="U20" s="16" t="n"/>
-      <c r="V20" s="16" t="n"/>
-      <c r="W20" s="16" t="n"/>
-      <c r="X20" s="16" t="n"/>
+      <c r="A20" s="77" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B20" s="72" t="inlineStr">
+        <is>
+          <t>何达尔罕</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D20" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E20" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F20" s="73">
+        <f>G20+H20</f>
+        <v/>
+      </c>
+      <c r="G20" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="73">
+        <f>R20</f>
+        <v/>
+      </c>
+      <c r="I20" s="73" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J20" s="73" t="n">
+        <v>8900</v>
+      </c>
+      <c r="K20" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="73" t="n">
+        <v>8900</v>
+      </c>
+      <c r="M20" s="74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V20" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W20" s="72" t="n"/>
+      <c r="X20" s="72" t="n"/>
       <c r="Y20" s="16" t="n"/>
       <c r="Z20" s="16" t="n"/>
       <c r="AA20" s="16" t="n"/>
@@ -41781,30 +41943,84 @@
       <c r="AO20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
-      <c r="M21" s="16" t="n"/>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="16" t="n"/>
-      <c r="S21" s="16" t="n"/>
-      <c r="T21" s="16" t="n"/>
-      <c r="U21" s="16" t="n"/>
-      <c r="V21" s="16" t="n"/>
-      <c r="W21" s="16" t="n"/>
-      <c r="X21" s="16" t="n"/>
+      <c r="A21" s="77" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B21" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D21" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E21" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F21" s="73">
+        <f>G21+H21</f>
+        <v/>
+      </c>
+      <c r="G21" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="73">
+        <f>R21</f>
+        <v/>
+      </c>
+      <c r="I21" s="73" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J21" s="73" t="n">
+        <v>280430</v>
+      </c>
+      <c r="K21" s="73" t="n">
+        <v>35526.4</v>
+      </c>
+      <c r="L21" s="73" t="n">
+        <v>244903.6</v>
+      </c>
+      <c r="M21" s="74" t="n">
+        <v>1.032607</v>
+      </c>
+      <c r="N21" s="73" t="n">
+        <v>71261</v>
+      </c>
+      <c r="O21" s="73" t="n">
+        <v>6382.5</v>
+      </c>
+      <c r="P21" s="73" t="n">
+        <v>64878.5</v>
+      </c>
+      <c r="Q21" s="75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R21" s="73" t="n">
+        <v>15489.105</v>
+      </c>
+      <c r="S21" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V21" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W21" s="72" t="n"/>
+      <c r="X21" s="72" t="n"/>
       <c r="Y21" s="16" t="n"/>
       <c r="Z21" s="16" t="n"/>
       <c r="AA21" s="16" t="n"/>
@@ -41824,30 +42040,84 @@
       <c r="AO21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="16" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="16" t="n"/>
-      <c r="S22" s="16" t="n"/>
-      <c r="T22" s="16" t="n"/>
-      <c r="U22" s="16" t="n"/>
-      <c r="V22" s="16" t="n"/>
-      <c r="W22" s="16" t="n"/>
-      <c r="X22" s="16" t="n"/>
+      <c r="A22" s="77" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B22" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D22" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E22" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F22" s="73">
+        <f>G22+H22</f>
+        <v/>
+      </c>
+      <c r="G22" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H22" s="73">
+        <f>R22</f>
+        <v/>
+      </c>
+      <c r="I22" s="73" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J22" s="73" t="n">
+        <v>280035.6</v>
+      </c>
+      <c r="K22" s="73" t="n">
+        <v>87104.2</v>
+      </c>
+      <c r="L22" s="73" t="n">
+        <v>192931.4</v>
+      </c>
+      <c r="M22" s="74" t="n">
+        <v>1.04899643333333</v>
+      </c>
+      <c r="N22" s="73" t="n">
+        <v>139325.8</v>
+      </c>
+      <c r="O22" s="73" t="n">
+        <v>17558.27</v>
+      </c>
+      <c r="P22" s="73" t="n">
+        <v>121767.53</v>
+      </c>
+      <c r="Q22" s="75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R22" s="73" t="n">
+        <v>15734.9465</v>
+      </c>
+      <c r="S22" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V22" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W22" s="72" t="n"/>
+      <c r="X22" s="72" t="n"/>
       <c r="Y22" s="16" t="n"/>
       <c r="Z22" s="16" t="n"/>
       <c r="AA22" s="16" t="n"/>
@@ -41867,30 +42137,84 @@
       <c r="AO22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="16" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
-      <c r="M23" s="16" t="n"/>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="16" t="n"/>
-      <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="24" t="n"/>
-      <c r="R23" s="16" t="n"/>
-      <c r="S23" s="16" t="n"/>
-      <c r="T23" s="16" t="n"/>
-      <c r="U23" s="16" t="n"/>
-      <c r="V23" s="16" t="n"/>
-      <c r="W23" s="16" t="n"/>
-      <c r="X23" s="16" t="n"/>
+      <c r="A23" s="77" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B23" s="72" t="inlineStr">
+        <is>
+          <t>何达尔罕</t>
+        </is>
+      </c>
+      <c r="C23" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D23" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E23" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F23" s="73">
+        <f>G23+H23</f>
+        <v/>
+      </c>
+      <c r="G23" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H23" s="73">
+        <f>R23</f>
+        <v/>
+      </c>
+      <c r="I23" s="73" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J23" s="73" t="n">
+        <v>9650</v>
+      </c>
+      <c r="K23" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="73" t="n">
+        <v>9650</v>
+      </c>
+      <c r="M23" s="74" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="N23" s="73" t="n">
+        <v>11385</v>
+      </c>
+      <c r="O23" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="73" t="n">
+        <v>11385</v>
+      </c>
+      <c r="Q23" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V23" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W23" s="72" t="n"/>
+      <c r="X23" s="72" t="n"/>
       <c r="Y23" s="16" t="n"/>
       <c r="Z23" s="16" t="n"/>
       <c r="AA23" s="16" t="n"/>
@@ -41910,30 +42234,84 @@
       <c r="AO23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="16" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16" t="n"/>
-      <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="16" t="n"/>
-      <c r="S24" s="16" t="n"/>
-      <c r="T24" s="16" t="n"/>
-      <c r="U24" s="16" t="n"/>
-      <c r="V24" s="16" t="n"/>
-      <c r="W24" s="16" t="n"/>
-      <c r="X24" s="16" t="n"/>
+      <c r="A24" s="77" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B24" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C24" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D24" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E24" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F24" s="73">
+        <f>G24+H24</f>
+        <v/>
+      </c>
+      <c r="G24" s="73" t="n">
+        <v>1573.47670250896</v>
+      </c>
+      <c r="H24" s="73">
+        <f>R24</f>
+        <v/>
+      </c>
+      <c r="I24" s="73" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J24" s="73" t="n">
+        <v>395298.6</v>
+      </c>
+      <c r="K24" s="73" t="n">
+        <v>5085.75</v>
+      </c>
+      <c r="L24" s="73" t="n">
+        <v>390212.85</v>
+      </c>
+      <c r="M24" s="74" t="n">
+        <v>1.933835</v>
+      </c>
+      <c r="N24" s="73" t="n">
+        <v>15892.5</v>
+      </c>
+      <c r="O24" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="73" t="n">
+        <v>15892.5</v>
+      </c>
+      <c r="Q24" s="75" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="R24" s="73" t="n">
+        <v>26396.84775</v>
+      </c>
+      <c r="S24" s="73" t="n">
+        <v>78.67383512544799</v>
+      </c>
+      <c r="T24" s="74" t="n">
+        <v>0.78673835125448</v>
+      </c>
+      <c r="U24" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V24" s="73" t="n">
+        <v>1573.47670250896</v>
+      </c>
+      <c r="W24" s="72" t="n"/>
+      <c r="X24" s="72" t="n"/>
       <c r="Y24" s="16" t="n"/>
       <c r="Z24" s="16" t="n"/>
       <c r="AA24" s="16" t="n"/>
@@ -41953,30 +42331,84 @@
       <c r="AO24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
-      <c r="M25" s="16" t="n"/>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="16" t="n"/>
-      <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="24" t="n"/>
-      <c r="R25" s="16" t="n"/>
-      <c r="S25" s="16" t="n"/>
-      <c r="T25" s="16" t="n"/>
-      <c r="U25" s="16" t="n"/>
-      <c r="V25" s="16" t="n"/>
-      <c r="W25" s="16" t="n"/>
-      <c r="X25" s="16" t="n"/>
+      <c r="A25" s="77" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B25" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C25" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E25" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F25" s="73">
+        <f>G25+H25</f>
+        <v/>
+      </c>
+      <c r="G25" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H25" s="73">
+        <f>R25</f>
+        <v/>
+      </c>
+      <c r="I25" s="73" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J25" s="73" t="n">
+        <v>389024.9</v>
+      </c>
+      <c r="K25" s="73" t="n">
+        <v>54315</v>
+      </c>
+      <c r="L25" s="73" t="n">
+        <v>334709.9</v>
+      </c>
+      <c r="M25" s="74" t="n">
+        <v>1.95828285714286</v>
+      </c>
+      <c r="N25" s="73" t="n">
+        <v>76529.5</v>
+      </c>
+      <c r="O25" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="73" t="n">
+        <v>76529.5</v>
+      </c>
+      <c r="Q25" s="75" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="R25" s="73" t="n">
+        <v>26730.561</v>
+      </c>
+      <c r="S25" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V25" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W25" s="72" t="n"/>
+      <c r="X25" s="72" t="n"/>
       <c r="Y25" s="16" t="n"/>
       <c r="Z25" s="16" t="n"/>
       <c r="AA25" s="16" t="n"/>
@@ -41996,30 +42428,105 @@
       <c r="AO25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
-      <c r="M26" s="16" t="n"/>
-      <c r="N26" s="16" t="n"/>
-      <c r="O26" s="16" t="n"/>
-      <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="24" t="n"/>
-      <c r="R26" s="16" t="n"/>
-      <c r="S26" s="16" t="n"/>
-      <c r="T26" s="16" t="n"/>
-      <c r="U26" s="16" t="n"/>
-      <c r="V26" s="16" t="n"/>
-      <c r="W26" s="16" t="n"/>
-      <c r="X26" s="16" t="n"/>
+      <c r="A26" s="77" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B26" s="72" t="inlineStr">
+        <is>
+          <t>周信宇</t>
+        </is>
+      </c>
+      <c r="C26" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D26" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E26" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F26" s="73">
+        <f>G26+H26</f>
+        <v/>
+      </c>
+      <c r="G26" s="73" t="n">
+        <v>900</v>
+      </c>
+      <c r="H26" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="J26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="K26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="L26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="M26" s="74" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="N26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="O26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="P26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="Q26" s="75" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="R26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="S26" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T26" s="74" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="U26" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V26" s="73" t="n">
+        <v>900</v>
+      </c>
+      <c r="W26" s="72" t="n"/>
+      <c r="X26" s="72" t="n"/>
       <c r="Y26" s="16" t="n"/>
       <c r="Z26" s="16" t="n"/>
       <c r="AA26" s="16" t="n"/>
@@ -42039,30 +42546,84 @@
       <c r="AO26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-      <c r="M27" s="16" t="n"/>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="16" t="n"/>
-      <c r="P27" s="16" t="n"/>
-      <c r="Q27" s="24" t="n"/>
-      <c r="R27" s="16" t="n"/>
-      <c r="S27" s="16" t="n"/>
-      <c r="T27" s="16" t="n"/>
-      <c r="U27" s="16" t="n"/>
-      <c r="V27" s="16" t="n"/>
-      <c r="W27" s="16" t="n"/>
-      <c r="X27" s="16" t="n"/>
+      <c r="A27" s="77" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B27" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C27" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D27" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E27" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F27" s="73">
+        <f>G27+H27</f>
+        <v/>
+      </c>
+      <c r="G27" s="73" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H27" s="73">
+        <f>R27</f>
+        <v/>
+      </c>
+      <c r="I27" s="73" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J27" s="73" t="n">
+        <v>284935</v>
+      </c>
+      <c r="K27" s="73" t="n">
+        <v>36110</v>
+      </c>
+      <c r="L27" s="73" t="n">
+        <v>248825</v>
+      </c>
+      <c r="M27" s="74" t="n">
+        <v>1.00051923076923</v>
+      </c>
+      <c r="N27" s="73" t="n">
+        <v>11310</v>
+      </c>
+      <c r="O27" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="73" t="n">
+        <v>11310</v>
+      </c>
+      <c r="Q27" s="75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R27" s="73" t="n">
+        <v>13006.75</v>
+      </c>
+      <c r="S27" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="T27" s="74" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U27" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V27" s="73" t="n">
+        <v>1700</v>
+      </c>
+      <c r="W27" s="72" t="n"/>
+      <c r="X27" s="72" t="n"/>
       <c r="Y27" s="16" t="n"/>
       <c r="Z27" s="16" t="n"/>
       <c r="AA27" s="16" t="n"/>
@@ -42082,30 +42643,84 @@
       <c r="AO27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="24" t="n"/>
-      <c r="R28" s="16" t="n"/>
-      <c r="S28" s="16" t="n"/>
-      <c r="T28" s="16" t="n"/>
-      <c r="U28" s="16" t="n"/>
-      <c r="V28" s="16" t="n"/>
-      <c r="W28" s="16" t="n"/>
-      <c r="X28" s="16" t="n"/>
+      <c r="A28" s="77" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B28" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C28" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D28" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E28" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F28" s="73">
+        <f>G28+H28</f>
+        <v/>
+      </c>
+      <c r="G28" s="73" t="n">
+        <v>2550</v>
+      </c>
+      <c r="H28" s="73">
+        <f>R28</f>
+        <v/>
+      </c>
+      <c r="I28" s="73" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J28" s="73" t="n">
+        <v>324735</v>
+      </c>
+      <c r="K28" s="73" t="n">
+        <v>16680</v>
+      </c>
+      <c r="L28" s="73" t="n">
+        <v>308055</v>
+      </c>
+      <c r="M28" s="74" t="n">
+        <v>1.30785076923077</v>
+      </c>
+      <c r="N28" s="73" t="n">
+        <v>40051</v>
+      </c>
+      <c r="O28" s="73" t="n">
+        <v>8064.8</v>
+      </c>
+      <c r="P28" s="73" t="n">
+        <v>31986.2</v>
+      </c>
+      <c r="Q28" s="75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="R28" s="73" t="n">
+        <v>20402.472</v>
+      </c>
+      <c r="S28" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="T28" s="74" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U28" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V28" s="73" t="n">
+        <v>2550</v>
+      </c>
+      <c r="W28" s="72" t="n"/>
+      <c r="X28" s="72" t="n"/>
       <c r="Y28" s="16" t="n"/>
       <c r="Z28" s="16" t="n"/>
       <c r="AA28" s="16" t="n"/>
@@ -42125,30 +42740,86 @@
       <c r="AO28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
-      <c r="M29" s="16" t="n"/>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16" t="n"/>
-      <c r="P29" s="16" t="n"/>
-      <c r="Q29" s="24" t="n"/>
-      <c r="R29" s="16" t="n"/>
-      <c r="S29" s="16" t="n"/>
-      <c r="T29" s="16" t="n"/>
-      <c r="U29" s="16" t="n"/>
-      <c r="V29" s="16" t="n"/>
-      <c r="W29" s="16" t="n"/>
-      <c r="X29" s="16" t="n"/>
+      <c r="A29" s="77" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B29" s="72" t="inlineStr">
+        <is>
+          <t>周信宇</t>
+        </is>
+      </c>
+      <c r="C29" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D29" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E29" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F29" s="73">
+        <f>G29+H29</f>
+        <v/>
+      </c>
+      <c r="G29" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H29" s="73">
+        <f>R29</f>
+        <v/>
+      </c>
+      <c r="I29" s="73" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J29" s="73" t="n">
+        <v>8800</v>
+      </c>
+      <c r="K29" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="73" t="n">
+        <v>8800</v>
+      </c>
+      <c r="M29" s="74" t="n">
+        <v>0.293333333333333</v>
+      </c>
+      <c r="N29" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T29" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V29" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W29" s="72" t="n"/>
+      <c r="X29" s="72" t="n"/>
       <c r="Y29" s="16" t="n"/>
       <c r="Z29" s="16" t="n"/>
       <c r="AA29" s="16" t="n"/>
@@ -42168,30 +42839,84 @@
       <c r="AO29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16" t="n"/>
-      <c r="P30" s="16" t="n"/>
-      <c r="Q30" s="24" t="n"/>
-      <c r="R30" s="16" t="n"/>
-      <c r="S30" s="16" t="n"/>
-      <c r="T30" s="16" t="n"/>
-      <c r="U30" s="16" t="n"/>
-      <c r="V30" s="16" t="n"/>
-      <c r="W30" s="16" t="n"/>
-      <c r="X30" s="16" t="n"/>
+      <c r="A30" s="77" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B30" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C30" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D30" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E30" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F30" s="73">
+        <f>G30+H30</f>
+        <v/>
+      </c>
+      <c r="G30" s="73" t="n">
+        <v>1580</v>
+      </c>
+      <c r="H30" s="73">
+        <f>R30</f>
+        <v/>
+      </c>
+      <c r="I30" s="73" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J30" s="73" t="n">
+        <v>286650</v>
+      </c>
+      <c r="K30" s="73" t="n">
+        <v>48062.5</v>
+      </c>
+      <c r="L30" s="73" t="n">
+        <v>238587.5</v>
+      </c>
+      <c r="M30" s="74" t="n">
+        <v>1.02529807692308</v>
+      </c>
+      <c r="N30" s="73" t="n">
+        <v>27990</v>
+      </c>
+      <c r="O30" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="73" t="n">
+        <v>27990</v>
+      </c>
+      <c r="Q30" s="75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R30" s="73" t="n">
+        <v>13328.875</v>
+      </c>
+      <c r="S30" s="73" t="n">
+        <v>79</v>
+      </c>
+      <c r="T30" s="74" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U30" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V30" s="73" t="n">
+        <v>1580</v>
+      </c>
+      <c r="W30" s="72" t="n"/>
+      <c r="X30" s="72" t="n"/>
       <c r="Y30" s="16" t="n"/>
       <c r="Z30" s="16" t="n"/>
       <c r="AA30" s="16" t="n"/>
@@ -42211,30 +42936,84 @@
       <c r="AO30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
-      <c r="M31" s="16" t="n"/>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="16" t="n"/>
-      <c r="P31" s="16" t="n"/>
-      <c r="Q31" s="24" t="n"/>
-      <c r="R31" s="16" t="n"/>
-      <c r="S31" s="16" t="n"/>
-      <c r="T31" s="16" t="n"/>
-      <c r="U31" s="16" t="n"/>
-      <c r="V31" s="16" t="n"/>
-      <c r="W31" s="16" t="n"/>
-      <c r="X31" s="16" t="n"/>
+      <c r="A31" s="77" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B31" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C31" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D31" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E31" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F31" s="73">
+        <f>G31+H31</f>
+        <v/>
+      </c>
+      <c r="G31" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H31" s="73">
+        <f>R31</f>
+        <v/>
+      </c>
+      <c r="I31" s="73" t="n">
+        <v>260000</v>
+      </c>
+      <c r="J31" s="73" t="n">
+        <v>247544</v>
+      </c>
+      <c r="K31" s="73" t="n">
+        <v>39700</v>
+      </c>
+      <c r="L31" s="73" t="n">
+        <v>207844</v>
+      </c>
+      <c r="M31" s="74" t="n">
+        <v>0.918692307692308</v>
+      </c>
+      <c r="N31" s="73" t="n">
+        <v>31016</v>
+      </c>
+      <c r="O31" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="73" t="n">
+        <v>31016</v>
+      </c>
+      <c r="Q31" s="75" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R31" s="73" t="n">
+        <v>8360.1</v>
+      </c>
+      <c r="S31" s="73" t="n">
+        <v>97</v>
+      </c>
+      <c r="T31" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V31" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W31" s="72" t="n"/>
+      <c r="X31" s="72" t="n"/>
       <c r="Y31" s="16" t="n"/>
       <c r="Z31" s="16" t="n"/>
       <c r="AA31" s="16" t="n"/>
@@ -42254,30 +43033,86 @@
       <c r="AO31" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
-      <c r="M32" s="16" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="24" t="n"/>
-      <c r="R32" s="16" t="n"/>
-      <c r="S32" s="16" t="n"/>
-      <c r="T32" s="16" t="n"/>
-      <c r="U32" s="16" t="n"/>
-      <c r="V32" s="16" t="n"/>
-      <c r="W32" s="16" t="n"/>
-      <c r="X32" s="16" t="n"/>
+      <c r="A32" s="77" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B32" s="72" t="inlineStr">
+        <is>
+          <t>周信宇</t>
+        </is>
+      </c>
+      <c r="C32" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D32" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E32" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F32" s="73">
+        <f>G32+H32</f>
+        <v/>
+      </c>
+      <c r="G32" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H32" s="73">
+        <f>R32</f>
+        <v/>
+      </c>
+      <c r="I32" s="73" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J32" s="73" t="n">
+        <v>32190</v>
+      </c>
+      <c r="K32" s="73" t="n">
+        <v>8800</v>
+      </c>
+      <c r="L32" s="73" t="n">
+        <v>23390</v>
+      </c>
+      <c r="M32" s="74" t="n">
+        <v>0.58475</v>
+      </c>
+      <c r="N32" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R32" s="73" t="n">
+        <v>233.9</v>
+      </c>
+      <c r="S32" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T32" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V32" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W32" s="72" t="n"/>
+      <c r="X32" s="72" t="n"/>
       <c r="Y32" s="16" t="n"/>
       <c r="Z32" s="16" t="n"/>
       <c r="AA32" s="16" t="n"/>
@@ -42297,30 +43132,105 @@
       <c r="AO32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
-      <c r="M33" s="16" t="n"/>
-      <c r="N33" s="16" t="n"/>
-      <c r="O33" s="16" t="n"/>
-      <c r="P33" s="16" t="n"/>
-      <c r="Q33" s="24" t="n"/>
-      <c r="R33" s="16" t="n"/>
-      <c r="S33" s="16" t="n"/>
-      <c r="T33" s="16" t="n"/>
-      <c r="U33" s="16" t="n"/>
-      <c r="V33" s="16" t="n"/>
-      <c r="W33" s="16" t="n"/>
-      <c r="X33" s="16" t="n"/>
+      <c r="A33" s="77" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B33" s="72" t="inlineStr">
+        <is>
+          <t>王沛贤</t>
+        </is>
+      </c>
+      <c r="C33" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D33" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E33" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F33" s="73">
+        <f>G33+H33</f>
+        <v/>
+      </c>
+      <c r="G33" s="73" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H33" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="J33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="K33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="L33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="M33" s="74" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="N33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="O33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="P33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="Q33" s="75" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="R33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="S33" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T33" s="74" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="U33" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V33" s="73" t="n">
+        <v>1160</v>
+      </c>
+      <c r="W33" s="72" t="n"/>
+      <c r="X33" s="72" t="n"/>
       <c r="Y33" s="16" t="n"/>
       <c r="Z33" s="16" t="n"/>
       <c r="AA33" s="16" t="n"/>
@@ -42340,30 +43250,84 @@
       <c r="AO33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
-      <c r="M34" s="16" t="n"/>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="16" t="n"/>
-      <c r="P34" s="16" t="n"/>
-      <c r="Q34" s="24" t="n"/>
-      <c r="R34" s="16" t="n"/>
-      <c r="S34" s="16" t="n"/>
-      <c r="T34" s="16" t="n"/>
-      <c r="U34" s="16" t="n"/>
-      <c r="V34" s="16" t="n"/>
-      <c r="W34" s="16" t="n"/>
-      <c r="X34" s="16" t="n"/>
+      <c r="A34" s="77" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B34" s="72" t="inlineStr">
+        <is>
+          <t>杨明</t>
+        </is>
+      </c>
+      <c r="C34" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D34" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E34" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F34" s="73">
+        <f>G34+H34</f>
+        <v/>
+      </c>
+      <c r="G34" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H34" s="73">
+        <f>R34</f>
+        <v/>
+      </c>
+      <c r="I34" s="73" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J34" s="73" t="n">
+        <v>157100</v>
+      </c>
+      <c r="K34" s="73" t="n">
+        <v>55570</v>
+      </c>
+      <c r="L34" s="73" t="n">
+        <v>101530</v>
+      </c>
+      <c r="M34" s="74" t="n">
+        <v>0.530519</v>
+      </c>
+      <c r="N34" s="73" t="n">
+        <v>57625.7</v>
+      </c>
+      <c r="O34" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="73" t="n">
+        <v>57625.7</v>
+      </c>
+      <c r="Q34" s="75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R34" s="73" t="n">
+        <v>3183.114</v>
+      </c>
+      <c r="S34" s="73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T34" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V34" s="73" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W34" s="72" t="n"/>
+      <c r="X34" s="72" t="n"/>
       <c r="Y34" s="16" t="n"/>
       <c r="Z34" s="16" t="n"/>
       <c r="AA34" s="16" t="n"/>
@@ -42383,30 +43347,84 @@
       <c r="AO34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
-      <c r="M35" s="16" t="n"/>
-      <c r="N35" s="16" t="n"/>
-      <c r="O35" s="16" t="n"/>
-      <c r="P35" s="16" t="n"/>
-      <c r="Q35" s="24" t="n"/>
-      <c r="R35" s="16" t="n"/>
-      <c r="S35" s="16" t="n"/>
-      <c r="T35" s="16" t="n"/>
-      <c r="U35" s="16" t="n"/>
-      <c r="V35" s="16" t="n"/>
-      <c r="W35" s="16" t="n"/>
-      <c r="X35" s="16" t="n"/>
+      <c r="A35" s="77" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B35" s="72" t="inlineStr">
+        <is>
+          <t>刘津玲</t>
+        </is>
+      </c>
+      <c r="C35" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D35" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E35" s="72" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F35" s="73">
+        <f>G35+H35</f>
+        <v/>
+      </c>
+      <c r="G35" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H35" s="73">
+        <f>R35</f>
+        <v/>
+      </c>
+      <c r="I35" s="73" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J35" s="73" t="n">
+        <v>246900</v>
+      </c>
+      <c r="K35" s="73" t="n">
+        <v>15517</v>
+      </c>
+      <c r="L35" s="73" t="n">
+        <v>231383</v>
+      </c>
+      <c r="M35" s="74" t="n">
+        <v>1.111013</v>
+      </c>
+      <c r="N35" s="73" t="n">
+        <v>113751.9</v>
+      </c>
+      <c r="O35" s="73" t="n">
+        <v>11831</v>
+      </c>
+      <c r="P35" s="73" t="n">
+        <v>101920.9</v>
+      </c>
+      <c r="Q35" s="75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R35" s="73" t="n">
+        <v>16665.195</v>
+      </c>
+      <c r="S35" s="73" t="n">
+        <v>94</v>
+      </c>
+      <c r="T35" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V35" s="73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W35" s="72" t="n"/>
+      <c r="X35" s="72" t="n"/>
       <c r="Y35" s="16" t="n"/>
       <c r="Z35" s="16" t="n"/>
       <c r="AA35" s="16" t="n"/>
@@ -42426,30 +43444,86 @@
       <c r="AO35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="16" t="n"/>
-      <c r="P36" s="16" t="n"/>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="16" t="n"/>
-      <c r="S36" s="16" t="n"/>
-      <c r="T36" s="16" t="n"/>
-      <c r="U36" s="16" t="n"/>
-      <c r="V36" s="16" t="n"/>
-      <c r="W36" s="16" t="n"/>
-      <c r="X36" s="16" t="n"/>
+      <c r="A36" s="77" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B36" s="72" t="inlineStr">
+        <is>
+          <t>周信宇</t>
+        </is>
+      </c>
+      <c r="C36" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D36" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E36" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F36" s="73">
+        <f>G36+H36</f>
+        <v/>
+      </c>
+      <c r="G36" s="73" t="n">
+        <v>3332</v>
+      </c>
+      <c r="H36" s="73">
+        <f>R36</f>
+        <v/>
+      </c>
+      <c r="I36" s="73" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J36" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="74" t="n">
+        <v>-0.3648</v>
+      </c>
+      <c r="N36" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="73" t="n">
+        <v>18240</v>
+      </c>
+      <c r="P36" s="73" t="n">
+        <v>-18240</v>
+      </c>
+      <c r="Q36" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T36" s="74" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U36" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V36" s="73" t="n">
+        <v>3332</v>
+      </c>
+      <c r="W36" s="72" t="n"/>
+      <c r="X36" s="72" t="n"/>
       <c r="Y36" s="16" t="n"/>
       <c r="Z36" s="16" t="n"/>
       <c r="AA36" s="16" t="n"/>
@@ -42469,30 +43543,105 @@
       <c r="AO36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
-      <c r="M37" s="16" t="n"/>
-      <c r="N37" s="16" t="n"/>
-      <c r="O37" s="16" t="n"/>
-      <c r="P37" s="16" t="n"/>
-      <c r="Q37" s="24" t="n"/>
-      <c r="R37" s="16" t="n"/>
-      <c r="S37" s="16" t="n"/>
-      <c r="T37" s="16" t="n"/>
-      <c r="U37" s="16" t="n"/>
-      <c r="V37" s="16" t="n"/>
-      <c r="W37" s="16" t="n"/>
-      <c r="X37" s="16" t="n"/>
+      <c r="A37" s="77" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B37" s="72" t="inlineStr">
+        <is>
+          <t>王沛贤</t>
+        </is>
+      </c>
+      <c r="C37" s="72" t="inlineStr">
+        <is>
+          <t>在职研</t>
+        </is>
+      </c>
+      <c r="D37" s="72" t="inlineStr">
+        <is>
+          <t>在职研项目部</t>
+        </is>
+      </c>
+      <c r="E37" s="72" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F37" s="73">
+        <f>G37+H37</f>
+        <v/>
+      </c>
+      <c r="G37" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H37" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="J37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="K37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="L37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="M37" s="74" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="N37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="O37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="P37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="Q37" s="75" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="R37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="S37" s="73" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="T37" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V37" s="73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W37" s="72" t="n"/>
+      <c r="X37" s="72" t="n"/>
       <c r="Y37" s="16" t="n"/>
       <c r="Z37" s="16" t="n"/>
       <c r="AA37" s="16" t="n"/>
